--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="498">
   <si>
     <t>Filename</t>
   </si>
@@ -808,679 +808,706 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9958,0.0001,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.0026,0.0001,0.0024,0.9978</t>
-  </si>
-  <si>
-    <t>0.9981,0.0001,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.0721,0.0001,0.0001,0.9854</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9945,0.0000,0.0035,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.9968,0.0000,0.0002,0.0018</t>
+  </si>
+  <si>
+    <t>0.1283,0.0000,0.0001,0.9789</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0005,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9296,0.0021,0.0486,0.0010</t>
+  </si>
+  <si>
+    <t>0.5147,0.0002,0.5827,0.0001</t>
+  </si>
+  <si>
+    <t>0.0302,0.0014,0.9857,0.0000</t>
+  </si>
+  <si>
+    <t>0.0089,0.0022,0.9877,0.0003</t>
+  </si>
+  <si>
+    <t>0.5641,0.0004,0.4733,0.0024</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9989,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.9950,0.0034,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9163,0.0006,0.0625,0.0014</t>
+  </si>
+  <si>
+    <t>0.0109,0.0029,0.9802,0.0013</t>
+  </si>
+  <si>
+    <t>0.0006,0.0004,0.9986,0.0004</t>
+  </si>
+  <si>
+    <t>0.0038,0.0006,0.9951,0.0002</t>
+  </si>
+  <si>
+    <t>0.1610,0.0001,0.9027,0.0001</t>
+  </si>
+  <si>
+    <t>0.0085,0.0003,0.9944,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9997,0.0010</t>
+  </si>
+  <si>
+    <t>0.2144,0.8485,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9631,0.0169,0.0076,0.0010</t>
+  </si>
+  <si>
+    <t>0.0003,0.0019,0.9993,0.0031</t>
+  </si>
+  <si>
+    <t>0.0018,0.9969,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.2576,0.0027,0.7083,0.0037</t>
+  </si>
+  <si>
+    <t>0.9180,0.1158,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9982,0.0065,0.0002</t>
+  </si>
+  <si>
+    <t>0.0059,0.0518,0.9649,0.0015</t>
+  </si>
+  <si>
+    <t>0.0031,0.0031,0.9742,0.0148</t>
+  </si>
+  <si>
+    <t>0.0022,0.0010,0.9959,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9975,0.0041</t>
+  </si>
+  <si>
+    <t>0.0001,0.0024,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9956,0.0055,0.0016</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0403,0.0006,0.9948</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.9908,0.0208,0.0038</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0033,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.0111,0.9950,0.0002</t>
+  </si>
+  <si>
+    <t>0.0067,0.0014,0.9900,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0009,0.9981,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0011,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0028,0.9997,0.0010</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0035,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0010,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.1511,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9993,0.0014</t>
+  </si>
+  <si>
+    <t>0.0000,0.9941,0.9887,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9991,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0031,0.9979,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9847,0.0016,0.0098,0.0001</t>
+  </si>
+  <si>
+    <t>0.9505,0.0060,0.0304,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0031,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9934,0.9910,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9955,0.0969,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9985,0.9234,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0002,0.0003,0.9989</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.0039,0.0000,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9990,0.0068,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9893,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9489,0.9848,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9654,0.9922,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9989,0.9715,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9897,0.9837,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9974,0.0015,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9960,0.0015,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.7860,0.0046,0.1700,0.0014</t>
-  </si>
-  <si>
-    <t>0.0235,0.0004,0.9818,0.0003</t>
-  </si>
-  <si>
-    <t>0.0612,0.0015,0.9629,0.0001</t>
-  </si>
-  <si>
-    <t>0.0038,0.0025,0.9936,0.0003</t>
-  </si>
-  <si>
-    <t>0.9736,0.0013,0.0165,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9986,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
+    <t>0.9990,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0035,0.0357,0.9903,0.0001</t>
+  </si>
+  <si>
+    <t>0.9915,0.0002,0.0057,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0007,0.0000</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.3893,0.0018,0.1466,0.0638</t>
-  </si>
-  <si>
-    <t>0.2775,0.0008,0.7561,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0183,0.0005,0.9847,0.0002</t>
-  </si>
-  <si>
-    <t>0.5703,0.0002,0.5787,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0003,0.9980,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9551,0.0412,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.1283,0.0095,0.8077,0.0032</t>
-  </si>
-  <si>
-    <t>0.0004,0.0013,0.9994,0.0021</t>
-  </si>
-  <si>
-    <t>0.0280,0.9605,0.0070,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0010,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0002,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9538,0.0558,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9992,0.0055,0.0001</t>
-  </si>
-  <si>
-    <t>0.0044,0.0271,0.9762,0.0009</t>
-  </si>
-  <si>
-    <t>0.0021,0.0008,0.9537,0.0573</t>
-  </si>
-  <si>
-    <t>0.0156,0.0123,0.9617,0.0009</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.9983,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.0239,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9975,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0008,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.0047,0.0624,0.0005,0.9897</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.9991,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0016,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.0555,0.9948,0.0000</t>
-  </si>
-  <si>
-    <t>0.4411,0.0017,0.5521,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0014,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0024,0.9965,0.0004</t>
-  </si>
-  <si>
-    <t>0.9976,0.0007,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9970,0.0015,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0010,0.9999,0.0013</t>
-  </si>
-  <si>
-    <t>0.9984,0.0007,0.0001,0.0001</t>
+    <t>0.0005,0.9989,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9989,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9311,0.1164,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0201,0.0014,0.9724,0.0043</t>
+  </si>
+  <si>
+    <t>0.7360,0.0020,0.2322,0.0001</t>
+  </si>
+  <si>
+    <t>0.4390,0.0007,0.5703,0.0037</t>
+  </si>
+  <si>
+    <t>0.0155,0.0010,0.9774,0.0028</t>
+  </si>
+  <si>
+    <t>0.0007,0.0009,0.0370,0.9899</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0024,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9851,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9990,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.8987,0.1062,0.0035,0.0001</t>
+  </si>
+  <si>
+    <t>0.8080,0.2094,0.0032,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0003,0.0002</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9988,0.0006,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9978,0.9737,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9998,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0034,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9991,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.9990,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9960,0.0004,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.9586,0.0028,0.0308,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0011,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.9748,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9931,0.2792,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.1878,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0001,0.0004,0.9988</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0014,0.0001,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9968,0.0168,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9864,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9605,0.9386,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9966,0.9608,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0962,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9978,0.2197,0.0001</t>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.4314,0.9751,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.2948,0.9960,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0007,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0019,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.5438,0.0029,0.4533,0.0016</t>
+  </si>
+  <si>
+    <t>0.9970,0.0000,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.9743,0.0026,0.0109,0.0003</t>
+  </si>
+  <si>
+    <t>0.5925,0.0000,0.0001,0.7848</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9925,0.9715,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0033,0.9945,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.3961,0.5358,0.0102,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.0029,0.0014,0.0006,0.9976</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0015,0.0036,0.9968,0.0012</t>
+  </si>
+  <si>
+    <t>0.9486,0.0000,0.0021,0.0459</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.4248,0.4412,0.0096,0.0014</t>
+  </si>
+  <si>
+    <t>0.9882,0.0025,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0709,0.8820,0.0068,0.0023</t>
+  </si>
+  <si>
+    <t>0.9149,0.0188,0.0393,0.0003</t>
+  </si>
+  <si>
+    <t>0.9661,0.0338,0.0003,0.0001</t>
   </si>
   <si>
     <t>0.9995,0.0001,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9993,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
+    <t>0.9993,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9966,0.0011,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9959,0.0010,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9553,0.0507,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.4835,0.4621,0.0118,0.0002</t>
+  </si>
+  <si>
+    <t>0.9731,0.0088,0.0049,0.0010</t>
+  </si>
+  <si>
+    <t>0.9632,0.0583,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9895,0.0036,0.0019,0.0011</t>
+  </si>
+  <si>
+    <t>0.9747,0.0085,0.0061,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9818,0.0024,0.0033,0.0024</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0061,0.9974,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.4706,0.0168,0.3347,0.0013</t>
+  </si>
+  <si>
+    <t>0.0000,0.0018,0.9999,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0001,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0034,0.0083,0.9938,0.0001</t>
-  </si>
-  <si>
-    <t>0.9689,0.0010,0.0221,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9982,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9469,0.0844,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.5840,0.0048,0.3245,0.0007</t>
-  </si>
-  <si>
-    <t>0.9395,0.0027,0.0417,0.0001</t>
-  </si>
-  <si>
-    <t>0.0442,0.0036,0.9501,0.0007</t>
-  </si>
-  <si>
-    <t>0.6875,0.0050,0.2298,0.0027</t>
-  </si>
-  <si>
-    <t>0.0031,0.0074,0.0065,0.9869</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.8690,0.9977,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.2207,0.7751,0.0098,0.0001</t>
-  </si>
-  <si>
-    <t>0.8963,0.0963,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.3779,0.8507,0.0025</t>
-  </si>
-  <si>
-    <t>0.0021,0.0226,0.9890,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0341,0.9975,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0008,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.9965,0.0001,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.0228,0.0029,0.9787,0.0004</t>
-  </si>
-  <si>
-    <t>0.9593,0.0001,0.0548,0.0001</t>
-  </si>
-  <si>
-    <t>0.7234,0.0024,0.3099,0.0005</t>
-  </si>
-  <si>
-    <t>0.0183,0.0000,0.0004,0.9951</t>
-  </si>
-  <si>
-    <t>0.0001,0.0016,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9951,0.9155,0.0000</t>
-  </si>
-  <si>
-    <t>0.0342,0.9699,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.2377,0.7319,0.0081,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.0001,0.0001,0.9992</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0073,0.0020,0.9870,0.0069</t>
-  </si>
-  <si>
-    <t>0.9961,0.0000,0.0002,0.0034</t>
-  </si>
-  <si>
-    <t>0.9989,0.0000,0.0000,0.0027</t>
-  </si>
-  <si>
-    <t>0.0034,0.9894,0.0049,0.0007</t>
-  </si>
-  <si>
-    <t>0.9946,0.0008,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9975,0.0001,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.2312,0.5876,0.0083,0.0071</t>
-  </si>
-  <si>
-    <t>0.9602,0.0075,0.0162,0.0002</t>
-  </si>
-  <si>
-    <t>0.9247,0.1113,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9973,0.0004,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0009,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0002,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9845,0.0113,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.8226,0.2281,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.1043,0.8843,0.0079,0.0002</t>
-  </si>
-  <si>
-    <t>0.0040,0.0219,0.9905,0.0003</t>
-  </si>
-  <si>
-    <t>0.9917,0.0098,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9966,0.0013,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9846,0.0068,0.0026,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0010,0.9999,0.0007</t>
-  </si>
-  <si>
-    <t>0.9698,0.0107,0.0033,0.0027</t>
+    <t>0.0002,0.0002,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0200,0.0015,0.9749,0.0010</t>
+  </si>
+  <si>
+    <t>0.0008,0.0002,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0035,0.0036,0.9923,0.0004</t>
+  </si>
+  <si>
+    <t>0.7633,0.0444,0.0809,0.0002</t>
+  </si>
+  <si>
+    <t>0.0122,0.6789,0.4249,0.0001</t>
+  </si>
+  <si>
+    <t>0.9858,0.0019,0.0044,0.0001</t>
+  </si>
+  <si>
+    <t>0.6794,0.0023,0.2570,0.0018</t>
+  </si>
+  <si>
+    <t>0.0106,0.0101,0.9802,0.0005</t>
+  </si>
+  <si>
+    <t>0.9165,0.1279,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0154,0.9813,0.0036,0.0001</t>
+  </si>
+  <si>
+    <t>0.9751,0.0364,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.6332,0.5905,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.5193,0.7135,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9689,0.0477,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9970,0.0002,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9907,0.0003,0.0016,0.0008</t>
+  </si>
+  <si>
+    <t>0.9284,0.0015,0.0499,0.0015</t>
+  </si>
+  <si>
+    <t>0.2280,0.0039,0.8343,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0044,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0018,0.9976,0.0001</t>
+  </si>
+  <si>
+    <t>0.0026,0.0015,0.9957,0.0002</t>
+  </si>
+  <si>
+    <t>0.0023,0.0079,0.9918,0.0004</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9967,0.0021,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0009,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0131,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.0141,0.0301,0.9341,0.0010</t>
+  </si>
+  <si>
+    <t>0.9974,0.0001,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0052,0.0008,0.9962,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0003,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.3132,0.9974,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.0002,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0008,0.0059,0.9976,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.0096,0.9911,0.0006</t>
-  </si>
-  <si>
-    <t>0.0002,0.0021,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0049,0.0005,0.9943,0.0002</t>
-  </si>
-  <si>
-    <t>0.0046,0.0004,0.9968,0.0001</t>
-  </si>
-  <si>
-    <t>0.1659,0.0026,0.8496,0.0033</t>
-  </si>
-  <si>
-    <t>0.1724,0.0294,0.5870,0.0004</t>
-  </si>
-  <si>
-    <t>0.0093,0.2116,0.8848,0.0001</t>
-  </si>
-  <si>
-    <t>0.9722,0.0026,0.0165,0.0001</t>
-  </si>
-  <si>
-    <t>0.6120,0.0033,0.3367,0.0019</t>
-  </si>
-  <si>
-    <t>0.0365,0.0184,0.9336,0.0032</t>
-  </si>
-  <si>
-    <t>0.0328,0.9754,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.9973,0.0022,0.0000</t>
-  </si>
-  <si>
-    <t>0.9746,0.0329,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9834,0.0293,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.7746,0.3911,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9931,0.0023,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9836,0.0006,0.0069,0.0006</t>
-  </si>
-  <si>
-    <t>0.9833,0.0005,0.0112,0.0004</t>
-  </si>
-  <si>
-    <t>0.9516,0.0015,0.0453,0.0003</t>
-  </si>
-  <si>
-    <t>0.0422,0.0005,0.9686,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0011,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0089,0.9964,0.0002</t>
-  </si>
-  <si>
-    <t>0.0194,0.0030,0.9704,0.0008</t>
-  </si>
-  <si>
-    <t>0.0018,0.0047,0.9940,0.0003</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9974,0.0008,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0017,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9958,0.0009,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.0006,0.0117,0.9986,0.0004</t>
-  </si>
-  <si>
-    <t>0.0362,0.5959,0.2537,0.0005</t>
-  </si>
-  <si>
-    <t>0.9846,0.0005,0.0091,0.0015</t>
-  </si>
-  <si>
-    <t>0.0178,0.0017,0.9896,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0011,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0310,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0009,0.9965,0.0006</t>
-  </si>
-  <si>
-    <t>0.0016,0.0009,0.9962,0.0011</t>
-  </si>
-  <si>
-    <t>0.9935,0.0002,0.0031,0.0000</t>
-  </si>
-  <si>
-    <t>0.9649,0.0002,0.0425,0.0001</t>
-  </si>
-  <si>
-    <t>0.9624,0.0006,0.0304,0.0018</t>
-  </si>
-  <si>
-    <t>0.9758,0.0283,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0008,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0030,0.9961,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0014,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0044,0.9977,0.0002</t>
-  </si>
-  <si>
-    <t>0.0020,0.0068,0.9930,0.0006</t>
-  </si>
-  <si>
-    <t>0.0014,0.0002,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.2426,0.0002,0.7837,0.0017</t>
-  </si>
-  <si>
-    <t>0.0446,0.0022,0.9512,0.0005</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9974,0.0026</t>
-  </si>
-  <si>
-    <t>0.9741,0.0000,0.0005,0.0380</t>
-  </si>
-  <si>
-    <t>0.0001,0.0722,0.0001,0.9991</t>
-  </si>
-  <si>
-    <t>0.0068,0.0000,0.0003,0.9976</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.7671,0.0153,0.0008,0.0888</t>
+    <t>0.0010,0.0006,0.9979,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0044,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0016,0.9980,0.0004</t>
+  </si>
+  <si>
+    <t>0.5980,0.0005,0.4748,0.0004</t>
+  </si>
+  <si>
+    <t>0.1550,0.0008,0.8794,0.0017</t>
+  </si>
+  <si>
+    <t>0.9796,0.0003,0.0250,0.0004</t>
+  </si>
+  <si>
+    <t>0.9983,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9888,0.0171,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0041,0.9963,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0045,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0055,0.0613,0.9469,0.0009</t>
+  </si>
+  <si>
+    <t>0.0024,0.0002,0.9980,0.0002</t>
+  </si>
+  <si>
+    <t>0.0070,0.0004,0.9923,0.0005</t>
+  </si>
+  <si>
+    <t>0.1089,0.0047,0.8126,0.0013</t>
+  </si>
+  <si>
+    <t>0.0012,0.0004,0.9974,0.0010</t>
+  </si>
+  <si>
+    <t>0.9650,0.0000,0.0001,0.1434</t>
+  </si>
+  <si>
+    <t>0.0001,0.0381,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.0078,0.0000,0.0001,0.9984</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0054,0.0132,0.0001,0.9947</t>
   </si>
 </sst>
 </file>
@@ -1866,7 +1893,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1880,7 +1907,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1894,7 +1921,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1908,7 +1935,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1922,7 +1949,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1936,7 +1963,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1950,7 +1977,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1964,7 +1991,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1978,7 +2005,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1992,7 +2019,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2006,7 +2033,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2020,7 +2047,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2034,7 +2061,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2045,10 +2072,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2062,7 +2089,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2076,7 +2103,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2090,7 +2117,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2104,7 +2131,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2118,7 +2145,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2132,7 +2159,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2146,7 +2173,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2160,7 +2187,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2174,7 +2201,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2188,7 +2215,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2202,7 +2229,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2216,7 +2243,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2230,7 +2257,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2244,7 +2271,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2258,7 +2285,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2269,10 +2296,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2283,10 +2310,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2300,7 +2327,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2314,7 +2341,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2328,7 +2355,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2339,10 +2366,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2356,7 +2383,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2370,7 +2397,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2384,7 +2411,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2398,7 +2425,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2412,7 +2439,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2426,7 +2453,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2440,7 +2467,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2454,7 +2481,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2468,7 +2495,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2482,7 +2509,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2496,7 +2523,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2510,7 +2537,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2524,7 +2551,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2538,7 +2565,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2552,7 +2579,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2566,7 +2593,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2580,7 +2607,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2594,7 +2621,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2608,7 +2635,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2622,7 +2649,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2636,7 +2663,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2650,7 +2677,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2664,7 +2691,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2678,7 +2705,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2692,7 +2719,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2706,7 +2733,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2717,10 +2744,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2734,7 +2761,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2748,7 +2775,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2762,7 +2789,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2776,7 +2803,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2790,7 +2817,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2804,7 +2831,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2818,7 +2845,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2832,7 +2859,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2846,7 +2873,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2860,7 +2887,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2874,7 +2901,7 @@
         <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2888,7 +2915,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2899,10 +2926,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2916,7 +2943,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2930,7 +2957,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2944,7 +2971,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2958,7 +2985,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2972,7 +2999,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2986,7 +3013,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3000,7 +3027,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3014,7 +3041,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3028,7 +3055,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3042,7 +3069,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3053,10 +3080,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3067,10 +3094,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3084,7 +3111,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>322</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3098,7 +3125,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3112,7 +3139,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3126,7 +3153,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3140,7 +3167,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3154,7 +3181,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3168,7 +3195,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3182,7 +3209,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3196,7 +3223,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>355</v>
+        <v>272</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3210,7 +3237,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>268</v>
+        <v>360</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3224,7 +3251,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>355</v>
+        <v>272</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3238,7 +3265,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>355</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3252,7 +3279,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>361</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3266,7 +3293,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>355</v>
+        <v>272</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3280,7 +3307,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>268</v>
+        <v>353</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3294,7 +3321,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>355</v>
+        <v>272</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3308,7 +3335,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3322,7 +3349,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3336,7 +3363,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3350,7 +3377,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3364,7 +3391,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>283</v>
+        <v>366</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3378,7 +3405,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>284</v>
+        <v>367</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3392,7 +3419,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3406,7 +3433,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3420,7 +3447,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3434,7 +3461,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3448,7 +3475,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3459,10 +3486,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3476,7 +3503,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3490,7 +3517,7 @@
         <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3501,10 +3528,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3518,7 +3545,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3532,7 +3559,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3546,7 +3573,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3560,7 +3587,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>371</v>
+        <v>284</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3574,7 +3601,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3588,7 +3615,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3599,10 +3626,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3616,7 +3643,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3630,7 +3657,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3644,7 +3671,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>350</v>
+        <v>385</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3658,7 +3685,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>322</v>
+        <v>386</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3672,7 +3699,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3686,7 +3713,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>322</v>
+        <v>388</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3700,7 +3727,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3714,7 +3741,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3728,7 +3755,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3742,7 +3769,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3756,7 +3783,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3770,7 +3797,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3784,7 +3811,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3798,7 +3825,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3809,10 +3836,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3826,7 +3853,7 @@
         <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3840,7 +3867,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3851,10 +3878,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3868,7 +3895,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3882,7 +3909,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3896,7 +3923,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3910,7 +3937,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3924,7 +3951,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3938,7 +3965,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3952,7 +3979,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3966,7 +3993,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3980,7 +4007,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3994,7 +4021,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4008,7 +4035,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4022,7 +4049,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4036,7 +4063,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4050,7 +4077,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4061,10 +4088,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D159" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4078,7 +4105,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4092,7 +4119,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4106,7 +4133,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4120,7 +4147,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4134,7 +4161,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4148,7 +4175,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4162,7 +4189,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4176,7 +4203,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4190,7 +4217,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>379</v>
+        <v>419</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4204,7 +4231,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4218,7 +4245,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4232,7 +4259,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4246,7 +4273,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>377</v>
+        <v>423</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4260,7 +4287,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4274,7 +4301,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4285,10 +4312,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D175" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4299,10 +4326,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4316,7 +4343,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4330,7 +4357,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4344,7 +4371,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>418</v>
+        <v>385</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4358,7 +4385,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4372,7 +4399,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4386,7 +4413,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4400,7 +4427,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4414,7 +4441,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4428,7 +4455,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4439,10 +4466,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D186" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4456,7 +4483,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4470,7 +4497,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>359</v>
+        <v>438</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4484,7 +4511,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4498,7 +4525,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4512,7 +4539,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4526,7 +4553,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4537,10 +4564,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4551,10 +4578,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4568,7 +4595,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4582,7 +4609,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4596,7 +4623,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4607,10 +4634,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4624,7 +4651,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4638,7 +4665,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4649,10 +4676,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D201" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4663,10 +4690,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D202" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4680,7 +4707,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4694,7 +4721,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4708,7 +4735,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4722,7 +4749,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4733,10 +4760,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4750,7 +4777,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4764,7 +4791,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4778,7 +4805,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4792,7 +4819,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4806,7 +4833,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4820,7 +4847,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4834,7 +4861,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4848,7 +4875,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4862,7 +4889,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>271</v>
+        <v>361</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4876,7 +4903,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4890,7 +4917,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4904,7 +4931,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4918,7 +4945,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>322</v>
+        <v>353</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4932,7 +4959,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4943,10 +4970,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4960,7 +4987,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4974,7 +5001,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4988,7 +5015,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5002,7 +5029,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5016,7 +5043,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>356</v>
+        <v>475</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5030,7 +5057,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5044,7 +5071,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5058,7 +5085,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5072,7 +5099,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5086,7 +5113,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5097,10 +5124,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5114,7 +5141,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5128,7 +5155,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5142,7 +5169,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>471</v>
+        <v>274</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5156,7 +5183,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5170,7 +5197,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>473</v>
+        <v>275</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5184,7 +5211,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>474</v>
+        <v>353</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5198,7 +5225,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>471</v>
+        <v>275</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5212,7 +5239,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5226,7 +5253,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5240,7 +5267,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5254,7 +5281,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>477</v>
+        <v>319</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5268,7 +5295,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5282,7 +5309,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5296,7 +5323,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5310,7 +5337,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5324,7 +5351,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5338,7 +5365,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5352,7 +5379,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5366,7 +5393,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5380,7 +5407,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5394,7 +5421,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5408,7 +5435,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5419,10 +5446,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
     </row>
   </sheetData>
